--- a/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsPersonal.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="394">
   <si>
     <t>Result</t>
   </si>
@@ -717,12 +717,523 @@
   </si>
   <si>
     <t>Sun Aug 02 21:31:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:19:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:20:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:21:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:22:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:23:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:24:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:24:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:25:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:26:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:27:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:28:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:29:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:30:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:32:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:33:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:34:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:35:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:36:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:38:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:39:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:39:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:41:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:41:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:45:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:46:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:47:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:49:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:50:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:51:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:52:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:53:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:54:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:55:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:56:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:57:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:58:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:59:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:01:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:02:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:04:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:06:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:08:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:09:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:15:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:16:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:18:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:19:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:20:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:21:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:23:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:24:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:25:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:27:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:28:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:30:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:31:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:33:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:35:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:36:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:37:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:38:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:40:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:40:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:41:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:42:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:44:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:46:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:47:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:48:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:49:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:50:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:52:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:53:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:56:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:58:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:59:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 01:59:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:02:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:03:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:05:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:06:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:07:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:08:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:09:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:10:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:11:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:13:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:15:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:17:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:18:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:20:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:21:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:23:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:24:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:25:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:26:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:27:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:27:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:28:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:29:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:30:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:31:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:32:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:33:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:34:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:36:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:37:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:39:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:40:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:43:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:46:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:47:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:48:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:49:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:50:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:53:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:54:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:55:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:57:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 02:59:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:02:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:04:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:05:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:06:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:09:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:12:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:13:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:14:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:15:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 03:16:29 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1095,17 +1606,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1145,7 +1656,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1174,7 +1685,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1203,7 +1714,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1235,7 +1746,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1267,7 +1778,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1299,7 +1810,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1331,7 +1842,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1364,16 +1875,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1413,7 +1924,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1436,7 +1947,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1459,7 +1970,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1482,7 +1993,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1508,7 +2019,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1534,7 +2045,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1557,7 +2068,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1580,7 +2091,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1603,7 +2114,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1626,7 +2137,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1649,7 +2160,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1672,7 +2183,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1695,7 +2206,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1718,7 +2229,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1738,7 +2249,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1764,7 +2275,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1787,7 +2298,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1827,7 +2338,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1872,15 +2383,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1917,7 +2428,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1943,7 +2454,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1966,7 +2477,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1992,7 +2503,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2018,7 +2529,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2044,7 +2555,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2079,17 +2590,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
-    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2138,7 +2649,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>315</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2161,7 +2672,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>150</v>
+        <v>316</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2187,7 +2698,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>317</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2213,7 +2724,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>318</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2239,7 +2750,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>319</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2265,7 +2776,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>320</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2288,7 +2799,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>321</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2314,7 +2825,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>322</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2340,7 +2851,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>323</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2366,7 +2877,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>324</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2392,7 +2903,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>159</v>
+        <v>325</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2415,7 +2926,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2441,7 +2952,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>327</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2467,7 +2978,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>328</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2493,7 +3004,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>329</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2519,7 +3030,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>164</v>
+        <v>330</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2548,7 +3059,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>165</v>
+        <v>331</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2577,7 +3088,7 @@
         <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>332</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2606,7 +3117,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>167</v>
+        <v>333</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2629,7 +3140,7 @@
         <v>115</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>334</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2658,7 +3169,7 @@
         <v>115</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>169</v>
+        <v>335</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2687,7 +3198,7 @@
         <v>115</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>336</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2713,7 +3224,7 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>337</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2742,7 +3253,7 @@
         <v>115</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>172</v>
+        <v>338</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2774,7 +3285,7 @@
         <v>115</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>173</v>
+        <v>339</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2803,7 +3314,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>174</v>
+        <v>340</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2832,7 +3343,7 @@
         <v>115</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>341</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2864,7 +3375,7 @@
         <v>115</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>176</v>
+        <v>342</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2893,7 +3404,7 @@
         <v>115</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>343</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2922,7 +3433,7 @@
         <v>115</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>344</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2951,7 +3462,7 @@
         <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>179</v>
+        <v>345</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2974,7 +3485,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>180</v>
+        <v>346</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3003,7 +3514,7 @@
         <v>115</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>347</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3032,7 +3543,7 @@
         <v>115</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>348</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3058,7 +3569,7 @@
         <v>115</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>349</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3087,7 +3598,7 @@
         <v>115</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>350</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3119,7 +3630,7 @@
         <v>115</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>185</v>
+        <v>351</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3148,7 +3659,7 @@
         <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>186</v>
+        <v>352</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3177,7 +3688,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>187</v>
+        <v>353</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3209,7 +3720,7 @@
         <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>188</v>
+        <v>354</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3238,7 +3749,7 @@
         <v>115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>189</v>
+        <v>355</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3267,7 +3778,7 @@
         <v>115</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>190</v>
+        <v>356</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3296,7 +3807,7 @@
         <v>115</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>357</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3319,7 +3830,7 @@
         <v>115</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>192</v>
+        <v>358</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3348,7 +3859,7 @@
         <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3377,7 +3888,7 @@
         <v>115</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>360</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3403,7 +3914,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3432,7 +3943,7 @@
         <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>196</v>
+        <v>362</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3464,7 +3975,7 @@
         <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>197</v>
+        <v>363</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3493,7 +4004,7 @@
         <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>198</v>
+        <v>364</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3522,7 +4033,7 @@
         <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>199</v>
+        <v>365</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3554,7 +4065,7 @@
         <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>200</v>
+        <v>366</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3574,10 +4085,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>218</v>
+        <v>367</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -3623,7 +4134,7 @@
         <v>115</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>368</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3646,7 +4157,7 @@
         <v>115</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>369</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -3692,7 +4203,7 @@
         <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>202</v>
+        <v>370</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3712,10 +4223,10 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>220</v>
+        <v>371</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -3761,7 +4272,7 @@
         <v>115</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>372</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -3787,7 +4298,7 @@
         <v>115</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>373</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -3813,7 +4324,7 @@
         <v>115</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>205</v>
+        <v>374</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -3849,14 +4360,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3890,7 +4401,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3913,7 +4424,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>377</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3936,7 +4447,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>378</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3959,7 +4470,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>379</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3982,7 +4493,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4002,10 +4513,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>221</v>
+        <v>381</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -4025,7 +4536,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>222</v>
+        <v>382</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -4044,8 +4555,8 @@
       <c r="A9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B9" t="s">
-        <v>223</v>
+      <c r="B9" t="s" s="1">
+        <v>383</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -4070,14 +4581,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4108,7 +4619,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4131,7 +4642,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>390</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4154,7 +4665,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4177,7 +4688,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>392</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4200,7 +4711,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>393</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4228,12 +4739,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4261,7 +4772,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
